--- a/.cursor/scratch/tax_turbo_parts/CC_LEDGER.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/CC_LEDGER.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2838,11 +2838,11 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>STATE FARM INSURANCE</t>
+          <t>STATE FARM INSURANCE (home share)</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>2124.79</v>
+        <v>1105.46</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>U1/U2</t>
+          <t>U1 50% / U2 50%</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -2861,207 +2861,207 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Feb two policies; Mar-Aug combined 50/50; none after Aug on this card</t>
+          <t>User 2026-09-18: bundled home+auto. Only home share on 524. Feb unbundled $157.53 home / $145.25 auto used as the ratio. Yellow until declarations. None Sep–Dec on Prime.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="11" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Prime 2351</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Feb-Aug</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>STATE FARM INSURANCE (auto share)</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>1019.33</v>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>personal auto</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Bundled car. Previously Geico. Not 524 Sch E.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Prime 2351</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>2025-02-11</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>GEICO *AUTO credit</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>-540.89</v>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>personal auto</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Unused Geico auto premium when switching to State Farm auto. Not 524 income.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Travelers (prior home carrier)</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>INSURANCE</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>No 2025 Travelers on Prime/Sapphire/BoA/Monarch. Home moved to State Farm in February.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>Checking 0203</t>
         </is>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="C65" s="11" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>ComEd Jacob Coley</t>
         </is>
       </c>
-      <c r="D65" s="12" t="n">
+      <c r="D68" s="12" t="n">
         <v>829.15</v>
       </c>
-      <c r="E65" s="11" t="inlineStr">
+      <c r="E68" s="11" t="inlineStr">
         <is>
           <t>ELECTRIC</t>
         </is>
       </c>
-      <c r="F65" s="11" t="inlineStr">
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>524 Unit 2</t>
         </is>
       </c>
-      <c r="G65" s="11" t="inlineStr">
+      <c r="G68" s="11" t="inlineStr">
         <is>
           <t>TBD-MEGAN</t>
         </is>
       </c>
-      <c r="H65" s="11" t="inlineStr">
+      <c r="H68" s="11" t="inlineStr">
         <is>
           <t>REMIND JACOB: double-check ComEd with Megan. Monarch Adv Plus ACH (not CC). Keep amounts until she confirms meters / any extra check.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="11" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>Checking 0203</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>ComEd Megan Gerrard</t>
         </is>
       </c>
-      <c r="D66" s="12" t="n">
+      <c r="D69" s="12" t="n">
         <v>1565.26</v>
       </c>
-      <c r="E66" s="11" t="inlineStr">
+      <c r="E69" s="11" t="inlineStr">
         <is>
           <t>ELECTRIC</t>
         </is>
       </c>
-      <c r="F66" s="11" t="inlineStr">
+      <c r="F69" s="11" t="inlineStr">
         <is>
           <t>524 Unit 1</t>
         </is>
       </c>
-      <c r="G66" s="11" t="inlineStr">
+      <c r="G69" s="11" t="inlineStr">
         <is>
           <t>TBD-MEGAN</t>
         </is>
       </c>
-      <c r="H66" s="11" t="inlineStr">
+      <c r="H69" s="11" t="inlineStr">
         <is>
           <t>REMIND JACOB: double-check ComEd with Megan. INDN Megan Gerrard on Jake checking. Keep amounts until confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Prime 2351</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>THE HOME DEPOT #1901</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>28.14</v>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>EXTERIOR REPAIRS</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>U1 50% / U2 50%</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>APPLIED</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>March HD 100% 524 repairs, then 50/50 U1/U2 → U2 $14.07 / U1 $14.07</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Prime 2351</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>THE HOME DEPOT #1901</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>50.75</v>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>EXTERIOR REPAIRS</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>U1 50% / U2 50%</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>APPLIED</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>March HD 100% 524 repairs, then 50/50 U1/U2 → U2 $25.38 / U1 $25.37</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Prime 2351</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>2025-03-22</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>THE HOME DEPOT #1901</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>93.95999999999999</v>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>EXTERIOR REPAIRS</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>U1 50% / U2 50%</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>APPLIED</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>March HD 100% 524 repairs, then 50/50 U1/U2 → U2 $46.98 / U1 $46.98</t>
         </is>
       </c>
     </row>
@@ -3073,16 +3073,16 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>HOMEDEPOT.COM</t>
+          <t>THE HOME DEPOT #1901</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>1185.8</v>
+        <v>28.14</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>March HD 100% 524 repairs, then 50/50 U1/U2 → U2 $592.90 / U1 $592.90</t>
+          <t>March HD 100% 524 repairs, then 50/50 U1/U2 → U2 $14.07 / U1 $14.07</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2025-03-15</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="D71" s="4" t="n">
-        <v>11.34</v>
+        <v>50.75</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -3141,87 +3141,87 @@
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $5.67 / U1 $5.67</t>
+          <t>March HD 100% 524 repairs, then 50/50 U1/U2 → U2 $25.38 / U1 $25.37</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>Prime 2351</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Prime 2351</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>THE HOME DEPOT #1901</t>
         </is>
       </c>
-      <c r="D72" s="6" t="n">
-        <v>11.34</v>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>personal</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>User 2026-09-18: remaining HD/Lowe's/IKEA 1/3 personal (by transaction).</t>
+      <c r="D72" s="4" t="n">
+        <v>93.95999999999999</v>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>EXTERIOR REPAIRS</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>U1 50% / U2 50%</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>March HD 100% 524 repairs, then 50/50 U1/U2 → U2 $46.98 / U1 $46.98</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="13" t="inlineStr">
-        <is>
-          <t>Prime 2351</t>
-        </is>
-      </c>
-      <c r="B73" s="13" t="inlineStr">
-        <is>
-          <t>2025-02-16</t>
-        </is>
-      </c>
-      <c r="C73" s="13" t="inlineStr">
-        <is>
-          <t>THE HOME DEPOT #1901</t>
-        </is>
-      </c>
-      <c r="D73" s="14" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="E73" s="13" t="inlineStr">
-        <is>
-          <t>827 Grove materials</t>
-        </is>
-      </c>
-      <c r="F73" s="13" t="inlineStr">
-        <is>
-          <t>827 Grove CapEx</t>
-        </is>
-      </c>
-      <c r="G73" s="13" t="inlineStr">
-        <is>
-          <t>GROVE-SPLIT</t>
-        </is>
-      </c>
-      <c r="H73" s="13" t="inlineStr">
-        <is>
-          <t>1/3 of txn. Pre-close materials — NOT folded into locked TY2025 CapEx $53,660.</t>
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Prime 2351</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>HOMEDEPOT.COM</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>1185.8</v>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>EXTERIOR REPAIRS</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>U1 50% / U2 50%</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>March HD 100% 524 repairs, then 50/50 U1/U2 → U2 $592.90 / U1 $592.90</t>
         </is>
       </c>
     </row>
@@ -3233,16 +3233,16 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-16</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>IKEA BOLINGBROOK</t>
+          <t>THE HOME DEPOT #1901</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>99.79000000000001</v>
+        <v>11.34</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $49.90 / U1 $49.89</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $5.67 / U1 $5.67</t>
         </is>
       </c>
     </row>
@@ -3273,16 +3273,16 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-16</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>IKEA BOLINGBROOK</t>
+          <t>THE HOME DEPOT #1901</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>99.79000000000001</v>
+        <v>11.34</v>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
@@ -3313,16 +3313,16 @@
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-16</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>IKEA BOLINGBROOK</t>
+          <t>THE HOME DEPOT #1901</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>99.79000000000001</v>
+        <v>11.33</v>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
@@ -3353,16 +3353,16 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>IKEA 471245314</t>
+          <t>IKEA BOLINGBROOK</t>
         </is>
       </c>
       <c r="D77" s="4" t="n">
-        <v>22</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $11.00 / U1 $11.00</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $49.90 / U1 $49.89</t>
         </is>
       </c>
     </row>
@@ -3393,16 +3393,16 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>IKEA 471245314</t>
+          <t>IKEA BOLINGBROOK</t>
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>21.99</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
@@ -3433,16 +3433,16 @@
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
         <is>
-          <t>IKEA 471245314</t>
+          <t>IKEA BOLINGBROOK</t>
         </is>
       </c>
       <c r="D79" s="14" t="n">
-        <v>21.99</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
@@ -3473,16 +3473,16 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>LOWES #01845</t>
+          <t>IKEA 471245314</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>18.57</v>
+        <v>22</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $9.29 / U1 $9.28</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $11.00 / U1 $11.00</t>
         </is>
       </c>
     </row>
@@ -3513,16 +3513,16 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>LOWES #01845</t>
+          <t>IKEA 471245314</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>18.56</v>
+        <v>21.99</v>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
@@ -3553,16 +3553,16 @@
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>LOWES #01845</t>
+          <t>IKEA 471245314</t>
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>18.56</v>
+        <v>21.99</v>
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
@@ -3593,16 +3593,16 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>THE HOME DEPOT #1901</t>
+          <t>LOWES #01845</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>78.79000000000001</v>
+        <v>18.57</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $39.40 / U1 $39.39</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $9.29 / U1 $9.28</t>
         </is>
       </c>
     </row>
@@ -3633,16 +3633,16 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>THE HOME DEPOT #1901</t>
+          <t>LOWES #01845</t>
         </is>
       </c>
       <c r="D84" s="6" t="n">
-        <v>78.79000000000001</v>
+        <v>18.56</v>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
@@ -3673,16 +3673,16 @@
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
         <is>
-          <t>THE HOME DEPOT #1901</t>
+          <t>LOWES #01845</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
-        <v>78.78</v>
+        <v>18.56</v>
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>0.36</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $0.18 / U1 $0.18</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $39.40 / U1 $39.39</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="D87" s="6" t="n">
-        <v>0.36</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>0.35</v>
+        <v>78.78</v>
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="D89" s="4" t="n">
-        <v>101.98</v>
+        <v>0.36</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $50.99 / U1 $50.99</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $0.18 / U1 $0.18</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="D90" s="6" t="n">
-        <v>101.98</v>
+        <v>0.36</v>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-04-20</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>101.98</v>
+        <v>0.35</v>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
@@ -3953,16 +3953,16 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>LOWES #01845</t>
+          <t>THE HOME DEPOT #1901</t>
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>69.73</v>
+        <v>101.98</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $34.87 / U1 $34.86</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $50.99 / U1 $50.99</t>
         </is>
       </c>
     </row>
@@ -3993,16 +3993,16 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>LOWES #01845</t>
+          <t>THE HOME DEPOT #1901</t>
         </is>
       </c>
       <c r="D93" s="6" t="n">
-        <v>69.73</v>
+        <v>101.98</v>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
@@ -4033,16 +4033,16 @@
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
         <is>
-          <t>LOWES #01845</t>
+          <t>THE HOME DEPOT #1901</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
-        <v>69.73</v>
+        <v>101.98</v>
       </c>
       <c r="E94" s="13" t="inlineStr">
         <is>
@@ -4073,16 +4073,16 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>THE HOME DEPOT #1901</t>
+          <t>LOWES #01845</t>
         </is>
       </c>
       <c r="D95" s="4" t="n">
-        <v>136.96</v>
+        <v>69.73</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $68.48 / U1 $68.48</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $34.87 / U1 $34.86</t>
         </is>
       </c>
     </row>
@@ -4113,16 +4113,16 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>THE HOME DEPOT #1901</t>
+          <t>LOWES #01845</t>
         </is>
       </c>
       <c r="D96" s="6" t="n">
-        <v>136.96</v>
+        <v>69.73</v>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
@@ -4153,16 +4153,16 @@
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
         <is>
-          <t>THE HOME DEPOT #1901</t>
+          <t>LOWES #01845</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>136.96</v>
+        <v>69.73</v>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>64.66</v>
+        <v>136.96</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $32.33 / U1 $32.33</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $68.48 / U1 $68.48</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="D99" s="6" t="n">
-        <v>64.66</v>
+        <v>136.96</v>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
@@ -4273,81 +4273,201 @@
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="C100" s="13" t="inlineStr">
+        <is>
+          <t>THE HOME DEPOT #1901</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="n">
+        <v>136.96</v>
+      </c>
+      <c r="E100" s="13" t="inlineStr">
+        <is>
+          <t>827 Grove materials</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="inlineStr">
+        <is>
+          <t>827 Grove CapEx</t>
+        </is>
+      </c>
+      <c r="G100" s="13" t="inlineStr">
+        <is>
+          <t>GROVE-SPLIT</t>
+        </is>
+      </c>
+      <c r="H100" s="13" t="inlineStr">
+        <is>
+          <t>1/3 of txn. Pre-close materials — NOT folded into locked TY2025 CapEx $53,660.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Prime 2351</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
           <t>2025-11-02</t>
         </is>
       </c>
-      <c r="C100" s="13" t="inlineStr">
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>THE HOME DEPOT #1901</t>
         </is>
       </c>
-      <c r="D100" s="14" t="n">
+      <c r="D101" s="4" t="n">
+        <v>64.66</v>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>EXTERIOR REPAIRS</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>U1 50% / U2 50%</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>APPLIED</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $32.33 / U1 $32.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Prime 2351</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>THE HOME DEPOT #1901</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="n">
+        <v>64.66</v>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>personal</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>EXCLUDED</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>User 2026-09-18: remaining HD/Lowe's/IKEA 1/3 personal (by transaction).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="13" t="inlineStr">
+        <is>
+          <t>Prime 2351</t>
+        </is>
+      </c>
+      <c r="B103" s="13" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="C103" s="13" t="inlineStr">
+        <is>
+          <t>THE HOME DEPOT #1901</t>
+        </is>
+      </c>
+      <c r="D103" s="14" t="n">
         <v>64.65000000000001</v>
       </c>
-      <c r="E100" s="13" t="inlineStr">
+      <c r="E103" s="13" t="inlineStr">
         <is>
           <t>827 Grove materials</t>
         </is>
       </c>
-      <c r="F100" s="13" t="inlineStr">
+      <c r="F103" s="13" t="inlineStr">
         <is>
           <t>827 Grove CapEx</t>
         </is>
       </c>
-      <c r="G100" s="13" t="inlineStr">
+      <c r="G103" s="13" t="inlineStr">
         <is>
           <t>GROVE-SPLIT</t>
         </is>
       </c>
-      <c r="H100" s="13" t="inlineStr">
+      <c r="H103" s="13" t="inlineStr">
         <is>
           <t>1/3 of txn. Pre-close materials — NOT folded into locked TY2025 CapEx $53,660.</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>Prime 2351</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>Prime 2351</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="C101" s="7" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>EXTRA SPACE 6720</t>
         </is>
       </c>
-      <c r="D101" s="8" t="n">
+      <c r="D104" s="8" t="n">
         <v>360</v>
       </c>
-      <c r="E101" s="7" t="inlineStr">
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>storage?</t>
         </is>
       </c>
-      <c r="F101" s="7" t="inlineStr">
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="G101" s="7" t="inlineStr">
+      <c r="G104" s="7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H101" s="7" t="inlineStr">
+      <c r="H104" s="7" t="inlineStr">
         <is>
           <t>Was in Prime HOME total. Not HD/Lowe's/IKEA — still HOLD.</t>
         </is>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>STATUS: APPLIED = monthly P&amp;L. EXCLUDED = personal. HOLD = still confirm. INVENTORY = Art Sales (not P&amp;L, not Cost total yet). TBD-MEGAN = ComEd — remind Jacob to ask Megan. GROVE-SPLIT = 827 materials, not locked $53,660.</t>
         </is>

--- a/.cursor/scratch/tax_turbo_parts/CC_LEDGER.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/CC_LEDGER.xlsx
@@ -2493,7 +2493,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Grove 8 orders</t>
+          <t>Jan/Mar/Apr/Jun/Jul/Aug/Sep</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>User example; Aug tagged Business in Monarch</t>
+          <t>User 2026-09-18: “grove orders” = Grove Collaborative, not 827 N Grove the house. 8 Prime charges → 524 Unit 2 SUPPLIES.</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $5.67 / U1 $5.67</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 N Grove the house (by transaction) → U2 $5.67 / U1 $5.67</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>827 Grove materials</t>
+          <t>827 N Grove the house (not Grove Collaborative)</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>1/3 of txn. Pre-close materials — NOT folded into locked TY2025 CapEx $53,660.</t>
+          <t>1/3 of txn for 827 N Grove the house. Pre-close materials — NOT Grove Collaborative supplies. NOT folded into locked TY2025 CapEx $53,660.</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $49.90 / U1 $49.89</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 N Grove the house (by transaction) → U2 $49.90 / U1 $49.89</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>827 Grove materials</t>
+          <t>827 N Grove the house (not Grove Collaborative)</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="H79" s="13" t="inlineStr">
         <is>
-          <t>1/3 of txn. Pre-close materials — NOT folded into locked TY2025 CapEx $53,660.</t>
+          <t>1/3 of txn for 827 N Grove the house. Pre-close materials — NOT Grove Collaborative supplies. NOT folded into locked TY2025 CapEx $53,660.</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $11.00 / U1 $11.00</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 N Grove the house (by transaction) → U2 $11.00 / U1 $11.00</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>827 Grove materials</t>
+          <t>827 N Grove the house (not Grove Collaborative)</t>
         </is>
       </c>
       <c r="F82" s="13" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="H82" s="13" t="inlineStr">
         <is>
-          <t>1/3 of txn. Pre-close materials — NOT folded into locked TY2025 CapEx $53,660.</t>
+          <t>1/3 of txn for 827 N Grove the house. Pre-close materials — NOT Grove Collaborative supplies. NOT folded into locked TY2025 CapEx $53,660.</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $9.29 / U1 $9.28</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 N Grove the house (by transaction) → U2 $9.29 / U1 $9.28</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>827 Grove materials</t>
+          <t>827 N Grove the house (not Grove Collaborative)</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="H85" s="13" t="inlineStr">
         <is>
-          <t>1/3 of txn. Pre-close materials — NOT folded into locked TY2025 CapEx $53,660.</t>
+          <t>1/3 of txn for 827 N Grove the house. Pre-close materials — NOT Grove Collaborative supplies. NOT folded into locked TY2025 CapEx $53,660.</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $39.40 / U1 $39.39</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 N Grove the house (by transaction) → U2 $39.40 / U1 $39.39</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>827 Grove materials</t>
+          <t>827 N Grove the house (not Grove Collaborative)</t>
         </is>
       </c>
       <c r="F88" s="13" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="H88" s="13" t="inlineStr">
         <is>
-          <t>1/3 of txn. Pre-close materials — NOT folded into locked TY2025 CapEx $53,660.</t>
+          <t>1/3 of txn for 827 N Grove the house. Pre-close materials — NOT Grove Collaborative supplies. NOT folded into locked TY2025 CapEx $53,660.</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $0.18 / U1 $0.18</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 N Grove the house (by transaction) → U2 $0.18 / U1 $0.18</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>827 Grove materials</t>
+          <t>827 N Grove the house (not Grove Collaborative)</t>
         </is>
       </c>
       <c r="F91" s="13" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H91" s="13" t="inlineStr">
         <is>
-          <t>1/3 of txn. Pre-close materials — NOT folded into locked TY2025 CapEx $53,660.</t>
+          <t>1/3 of txn for 827 N Grove the house. Pre-close materials — NOT Grove Collaborative supplies. NOT folded into locked TY2025 CapEx $53,660.</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $50.99 / U1 $50.99</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 N Grove the house (by transaction) → U2 $50.99 / U1 $50.99</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="E94" s="13" t="inlineStr">
         <is>
-          <t>827 Grove materials</t>
+          <t>827 N Grove the house (not Grove Collaborative)</t>
         </is>
       </c>
       <c r="F94" s="13" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="H94" s="13" t="inlineStr">
         <is>
-          <t>1/3 of txn. Pre-close materials — NOT folded into locked TY2025 CapEx $53,660.</t>
+          <t>1/3 of txn for 827 N Grove the house. Pre-close materials — NOT Grove Collaborative supplies. NOT folded into locked TY2025 CapEx $53,660.</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $34.87 / U1 $34.86</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 N Grove the house (by transaction) → U2 $34.87 / U1 $34.86</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>827 Grove materials</t>
+          <t>827 N Grove the house (not Grove Collaborative)</t>
         </is>
       </c>
       <c r="F97" s="13" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H97" s="13" t="inlineStr">
         <is>
-          <t>1/3 of txn. Pre-close materials — NOT folded into locked TY2025 CapEx $53,660.</t>
+          <t>1/3 of txn for 827 N Grove the house. Pre-close materials — NOT Grove Collaborative supplies. NOT folded into locked TY2025 CapEx $53,660.</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $68.48 / U1 $68.48</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 N Grove the house (by transaction) → U2 $68.48 / U1 $68.48</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>827 Grove materials</t>
+          <t>827 N Grove the house (not Grove Collaborative)</t>
         </is>
       </c>
       <c r="F100" s="13" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="H100" s="13" t="inlineStr">
         <is>
-          <t>1/3 of txn. Pre-close materials — NOT folded into locked TY2025 CapEx $53,660.</t>
+          <t>1/3 of txn for 827 N Grove the house. Pre-close materials — NOT Grove Collaborative supplies. NOT folded into locked TY2025 CapEx $53,660.</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>1/3 524 repairs / 1/3 personal / 1/3 827 Grove (by transaction) → U2 $32.33 / U1 $32.33</t>
+          <t>1/3 524 repairs / 1/3 personal / 1/3 827 N Grove the house (by transaction) → U2 $32.33 / U1 $32.33</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>827 Grove materials</t>
+          <t>827 N Grove the house (not Grove Collaborative)</t>
         </is>
       </c>
       <c r="F103" s="13" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="H103" s="13" t="inlineStr">
         <is>
-          <t>1/3 of txn. Pre-close materials — NOT folded into locked TY2025 CapEx $53,660.</t>
+          <t>1/3 of txn for 827 N Grove the house. Pre-close materials — NOT Grove Collaborative supplies. NOT folded into locked TY2025 CapEx $53,660.</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STATUS: APPLIED = monthly P&amp;L. EXCLUDED = personal. HOLD = still confirm. INVENTORY = Art Sales (not P&amp;L, not Cost total yet). TBD-MEGAN = ComEd — remind Jacob to ask Megan. GROVE-SPLIT = 827 materials, not locked $53,660.</t>
+          <t>STATUS: APPLIED = monthly P&amp;L. EXCLUDED = personal. HOLD = still confirm. INVENTORY = Art Sales (not P&amp;L, not Cost total yet). TBD-MEGAN = ComEd — remind Jacob to ask Megan. GROVE-SPLIT = 827 N Grove the house materials (not Grove Collaborative), not locked $53,660.</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/CC_LEDGER.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/CC_LEDGER.xlsx
@@ -2901,7 +2901,7 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Bundled car. Previously Geico. Not 524 Sch E.</t>
+          <t>Bundled car. User 2026-09-20: Geico was the cars. Not 524 Sch E. Not EPGC.</t>
         </is>
       </c>
     </row>
@@ -2941,47 +2941,47 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>Unused Geico auto premium when switching to State Farm auto. Not 524 income.</t>
+          <t>LOCKED 2026-09-20: Geico = cars / personal auto. Unused Geico auto premium when switching to State Farm auto. Not 524 INSURANCE. Not EPGC. Not 524 income.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>Travelers (prior home carrier)</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="n">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>2025-01 leftover</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Travelers (prior 524 home carrier)</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>INSURANCE</t>
         </is>
       </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>EXCLUDED</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>No 2025 Travelers on Prime/Sapphire/BoA/Monarch. Home moved to State Farm in February.</t>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>U1 50% / U2 50%</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>LOCKED 2026-09-20: Travelers was home insurance before for Ferdinand. Leftover 2025 (Jan leftover previously noted) is 524 INSURANCE, not auto. $0 cash on Prime/Sapphire/BoA/Monarch. Same 50/50 U1/U2 home-share mapping — do not invent a new split.</t>
         </is>
       </c>
     </row>
